--- a/ci-build/ValueSet-vs-oncobox-primaerfallart.xlsx
+++ b/ci-build/ValueSet-vs-oncobox-primaerfallart.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T14:42:03+00:00</t>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>Publisher</t>
